--- a/Results/Phase 2/Methanol/methanol climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results modified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Methanol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E157466-0BEC-4FA2-8FDE-3F3B53FC04E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB4E72A-0222-4F92-A620-79BE90677EED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17625" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="methanolBAU" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -688,7 +687,7 @@
         <v>0.18263883981556689</v>
       </c>
       <c r="F4">
-        <v>8.031337275181194E-2</v>
+        <v>8.0313372751812051E-2</v>
       </c>
       <c r="G4">
         <v>4.5723358992611089E-2</v>
@@ -782,7 +781,7 @@
         <v>0.17343411813392901</v>
       </c>
       <c r="F6">
-        <v>7.1876419065542263E-2</v>
+        <v>7.1876419065542374E-2</v>
       </c>
       <c r="G6">
         <v>1.323200409367942E-2</v>
@@ -876,7 +875,7 @@
         <v>0.16776440371140661</v>
       </c>
       <c r="F8">
-        <v>6.7389222396193216E-2</v>
+        <v>6.7389222396193327E-2</v>
       </c>
       <c r="G8">
         <v>1.516222820624147E-3</v>
@@ -1112,13 +1111,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>0.45226758301252512</v>
+        <v>0.41293989378254548</v>
       </c>
       <c r="E2">
         <v>0.1855477198404307</v>
       </c>
       <c r="F2">
-        <v>0.14266669974814639</v>
+        <v>0.17398399381729301</v>
       </c>
       <c r="G2">
         <v>5.0083301444749991E-2</v>
@@ -1145,7 +1144,7 @@
         <v>1.3687278827020769E-3</v>
       </c>
       <c r="O2">
-        <v>7.0644983299126232E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1159,13 +1158,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>0.44533573138207377</v>
+        <v>0.40761562968575649</v>
       </c>
       <c r="E3">
         <v>0.18382919060590239</v>
       </c>
       <c r="F3">
-        <v>0.13949668219245503</v>
+        <v>0.17242156368913233</v>
       </c>
       <c r="G3">
         <v>4.8214942313456438E-2</v>
@@ -1192,7 +1191,7 @@
         <v>1.280091146362091E-3</v>
       </c>
       <c r="O3">
-        <v>7.0644983192994615E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1206,13 +1205,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>0.43785569035991118</v>
+        <v>0.40240369504060042</v>
       </c>
       <c r="E4">
         <v>0.18263883981556689</v>
       </c>
       <c r="F4">
-        <v>0.13588374746649903</v>
+        <v>0.17107673524042441</v>
       </c>
       <c r="G4">
         <v>4.5723358992611089E-2</v>
@@ -1239,7 +1238,7 @@
         <v>1.1644470789067499E-3</v>
       </c>
       <c r="O4">
-        <v>7.0644983093236136E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1253,13 +1252,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>0.42765744410817907</v>
+        <v>0.39610045635422841</v>
       </c>
       <c r="E5">
         <v>0.18185032690763331</v>
       </c>
       <c r="F5">
-        <v>0.13070661019375374</v>
+        <v>0.16979460541310368</v>
       </c>
       <c r="G5">
         <v>4.1618575705759803E-2</v>
@@ -1286,7 +1285,7 @@
         <v>1.100141444635164E-3</v>
       </c>
       <c r="O5">
-        <v>7.0644982973300602E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -1300,13 +1299,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>0.35935301439883699</v>
+        <v>0.3495228100342862</v>
       </c>
       <c r="E6">
         <v>0.17343411813392901</v>
       </c>
       <c r="F6">
-        <v>0.10002529481824558</v>
+        <v>0.16084007254973434</v>
       </c>
       <c r="G6">
         <v>1.323200409367942E-2</v>
@@ -1333,7 +1332,7 @@
         <v>7.6932600294129442E-4</v>
       </c>
       <c r="O6">
-        <v>7.0644982096039546E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -1347,13 +1346,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>0.33443351889532758</v>
+        <v>0.331507965293313</v>
       </c>
       <c r="E7">
         <v>0.16929679867809069</v>
       </c>
       <c r="F7">
-        <v>8.8909223590436043E-2</v>
+        <v>0.1566286517444973</v>
       </c>
       <c r="G7">
         <v>4.0055926335307137E-3</v>
@@ -1380,7 +1379,7 @@
         <v>5.395976008691132E-4</v>
       </c>
       <c r="O7">
-        <v>7.0644981756075836E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -1394,13 +1393,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>0.32701717215059067</v>
+        <v>0.32568515534436682</v>
       </c>
       <c r="E8">
         <v>0.16776440371140661</v>
       </c>
       <c r="F8">
-        <v>8.5671353377364701E-2</v>
+        <v>0.15498431822112563</v>
       </c>
       <c r="G8">
         <v>1.516222820624147E-3</v>
@@ -1427,7 +1426,7 @@
         <v>4.547630681316607E-4</v>
       </c>
       <c r="O8">
-        <v>7.0644981649984784E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1441,13 +1440,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>0.42082471502299101</v>
+        <v>0.3914664290275745</v>
       </c>
       <c r="E9">
         <v>0.1807834979870836</v>
       </c>
       <c r="F9">
-        <v>0.12746926371854159</v>
+        <v>0.16875596060326398</v>
       </c>
       <c r="G9">
         <v>3.9122700718410543E-2</v>
@@ -1474,7 +1473,7 @@
         <v>1.1059876664443441E-3</v>
       </c>
       <c r="O9">
-        <v>7.0644982880138901E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1488,13 +1487,13 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>0.36706820532637729</v>
+        <v>0.35517983500175249</v>
       </c>
       <c r="E10">
         <v>0.1746507049116372</v>
       </c>
       <c r="F10">
-        <v>0.10292738773874108</v>
+        <v>0.16168399961560961</v>
       </c>
       <c r="G10">
         <v>1.6715262786883379E-2</v>
@@ -1521,7 +1520,7 @@
         <v>7.7153643287371785E-4</v>
       </c>
       <c r="O10">
-        <v>7.0644982201493345E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1535,13 +1534,13 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>0.33533231233616989</v>
+        <v>0.3331338647146303</v>
       </c>
       <c r="E11">
         <v>0.17058390276084601</v>
       </c>
       <c r="F11">
-        <v>8.9533829249794958E-2</v>
+        <v>0.15798036341733526</v>
       </c>
       <c r="G11">
         <v>2.8800845186845122E-3</v>
@@ -1568,7 +1567,7 @@
         <v>6.0263194716483957E-4</v>
       </c>
       <c r="O11">
-        <v>7.0644981789079894E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3351,7 +3350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83EDCF79-F7FA-443E-805F-76E57997BDC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A45D5A0-32AD-4075-8423-E327A6FA0128}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3394,13 +3393,13 @@
         <v>8.2860517459374894E-2</v>
       </c>
       <c r="D2" s="3">
-        <v>22.550325137004286</v>
+        <v>28.671696800263796</v>
       </c>
       <c r="E2" s="3">
-        <v>7.0644983299126232E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F2" s="3">
-        <v>0.14266669974814639</v>
+        <v>0.17398399381729301</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3414,13 +3413,13 @@
         <v>8.1385016141321098E-2</v>
       </c>
       <c r="D3" s="3">
-        <v>22.94519164078271</v>
+        <v>28.98427639282486</v>
       </c>
       <c r="E3" s="3">
-        <v>7.0644983192994615E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F3" s="3">
-        <v>0.13949668219245503</v>
+        <v>0.17242156368913233</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3431,16 +3430,16 @@
         <v>0.43829996735238053</v>
       </c>
       <c r="C4" s="3">
-        <v>8.031337275181194E-2</v>
+        <v>8.0313372751812051E-2</v>
       </c>
       <c r="D4" s="3">
-        <v>23.412434322997019</v>
+        <v>29.258832120958733</v>
       </c>
       <c r="E4" s="3">
-        <v>7.0644983093236136E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F4" s="3">
-        <v>0.13588374746649903</v>
+        <v>0.17107673524042441</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3454,13 +3453,13 @@
         <v>7.8875521244295366E-2</v>
       </c>
       <c r="D5" s="3">
-        <v>24.11613520712104</v>
+        <v>29.525475055390721</v>
       </c>
       <c r="E5" s="3">
-        <v>7.0644982973300602E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F5" s="3">
-        <v>0.13070661019375374</v>
+        <v>0.16979460541310368</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3471,16 +3470,16 @@
         <v>0.43829996702387158</v>
       </c>
       <c r="C6" s="3">
-        <v>7.1876419065542263E-2</v>
+        <v>7.1876419065542374E-2</v>
       </c>
       <c r="D6" s="3">
-        <v>29.342840079735101</v>
+        <v>31.532448882137786</v>
       </c>
       <c r="E6" s="3">
-        <v>7.0644982096039546E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F6" s="3">
-        <v>0.10002529481824558</v>
+        <v>0.16084007254973434</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3494,13 +3493,13 @@
         <v>6.8901204251102743E-2</v>
       </c>
       <c r="D7" s="3">
-        <v>31.843273752138927</v>
+        <v>32.573804324331988</v>
       </c>
       <c r="E7" s="3">
-        <v>7.0644981756075836E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F7" s="3">
-        <v>8.8909223590436043E-2</v>
+        <v>0.1566286517444973</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3511,16 +3510,16 @@
         <v>0.43829996691776457</v>
       </c>
       <c r="C8" s="3">
-        <v>6.7389222396193216E-2</v>
+        <v>6.7389222396193327E-2</v>
       </c>
       <c r="D8" s="3">
-        <v>32.653776953911155</v>
+        <v>32.999312042918092</v>
       </c>
       <c r="E8" s="3">
-        <v>7.0644981649984784E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F8" s="3">
-        <v>8.5671353377364701E-2</v>
+        <v>0.15498431822112563</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3534,13 +3533,13 @@
         <v>7.8605666823122033E-2</v>
       </c>
       <c r="D9" s="3">
-        <v>24.578078814625311</v>
+        <v>29.745070398135482</v>
       </c>
       <c r="E9" s="3">
-        <v>7.0644982880138901E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F9" s="3">
-        <v>0.12746926371854159</v>
+        <v>0.16875596060326398</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3554,13 +3553,13 @@
         <v>7.3981768222880884E-2</v>
       </c>
       <c r="D10" s="3">
-        <v>28.753390476707512</v>
+        <v>31.331728653143287</v>
       </c>
       <c r="E10" s="3">
-        <v>7.0644982201493345E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F10" s="3">
-        <v>0.10292738773874108</v>
+        <v>0.16168399961560961</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,13 +3573,13 @@
         <v>6.9961775679548699E-2</v>
       </c>
       <c r="D11" s="3">
-        <v>31.691529937573403</v>
+        <v>32.232150743389482</v>
       </c>
       <c r="E11" s="3">
-        <v>7.0644981789079894E-2</v>
+        <v>7.0644982438245726E-2</v>
       </c>
       <c r="F11" s="3">
-        <v>8.9533829249794958E-2</v>
+        <v>0.15798036341733526</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Methanol/methanol climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Methanol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB4E72A-0222-4F92-A620-79BE90677EED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A953066-69A0-4050-9419-B7810A738A34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17625" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17625" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="methanolBAU" sheetId="1" r:id="rId1"/>
@@ -171,6 +171,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -216,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -227,6 +228,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1577,10 +1579,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +1662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1737,7 +1742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1817,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1897,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1977,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2057,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2137,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2217,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2297,7 +2302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2377,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -2456,6 +2461,9 @@
       <c r="Z11">
         <v>0</v>
       </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA12" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2464,10 +2472,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2544,7 +2552,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2624,7 +2632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2704,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2784,7 +2792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2864,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2944,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3024,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3104,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3184,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3264,7 +3272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3343,6 +3351,9 @@
       <c r="Z11">
         <v>0</v>
       </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA12" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
